--- a/Experimenten_november7.xlsx
+++ b/Experimenten_november7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DAC9948072DBC2FBEFE9D797263319CD4D8AEC14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_DAC9948072DBC2FBEFE9D797263319CD4D8AEC14" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7F0B42F-C5DD-40FC-8994-3574B6D17F2F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="4965" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="26">
   <si>
     <t>t_max</t>
   </si>
@@ -102,11 +102,20 @@
   <si>
     <t>Aantal_runs</t>
   </si>
+  <si>
+    <t>Rekentijd Improving Search</t>
+  </si>
+  <si>
+    <t>Rekentijd SA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.00000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -136,13 +145,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -153,6 +219,54 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8CCF6FC2-AEC6-4A45-89C5-A983F2DC5AAC}" name="Table3" displayName="Table3" ref="B15:H27" totalsRowShown="0" tableBorderDxfId="3">
+  <autoFilter ref="B15:H27" xr:uid="{8CCF6FC2-AEC6-4A45-89C5-A983F2DC5AAC}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{35BFFC65-2930-4E5D-A214-A2427CBDA087}" name="t_max"/>
+    <tableColumn id="2" xr3:uid="{430AC80E-C9F7-478F-AB2C-F7643064C240}" name="temp"/>
+    <tableColumn id="3" xr3:uid="{0DD2E43C-0BEF-46F2-9684-9F53CD75D63B}" name="cooling_it"/>
+    <tableColumn id="4" xr3:uid="{22057C5A-AA3A-4995-8BB2-76C01D54F9D6}" name="cooling_factor" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{128A3944-CBC1-4117-B68F-321FD264BD25}" name="Random seed"/>
+    <tableColumn id="6" xr3:uid="{6AC219A4-C21C-411B-97C0-C2DCBF90A725}" name="Total penalty" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{2FBA85CD-40C6-45F6-842E-484B0E052752}" name="Totale rekentijd (s)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0618F307-BA82-4383-AB13-4DD1D1274DA4}" name="Table2" displayName="Table2" ref="F16:L21" totalsRowShown="0" tableBorderDxfId="8">
+  <autoFilter ref="F16:L21" xr:uid="{0618F307-BA82-4383-AB13-4DD1D1274DA4}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{646D0CFC-E6AB-46C4-9F0B-727BBF0F3310}" name="Random seed"/>
+    <tableColumn id="2" xr3:uid="{B17C9D9E-E81E-4D36-B64F-F863B2214EFA}" name="Aantal temperatuurverlagingen"/>
+    <tableColumn id="3" xr3:uid="{51CA0589-7970-4E49-8BF5-666C25DCC266}" name="Eindtemperatuur"/>
+    <tableColumn id="4" xr3:uid="{6C51C3C6-AA61-45A6-A134-E264BB52ED6E}" name="Penalty SA" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{485846F9-378A-4348-B481-C31BD3724CA2}" name="Total penalty" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{36F6874C-747F-49F4-9BFB-9B4090DC878A}" name="Rekentijd SA" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{9D1FBBDA-25D1-4CC1-810C-0EAD60D85718}" name="Rekentijd Improving Search" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -440,16 +554,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="10" width="20" customWidth="1"/>
+    <col min="2" max="2" width="8.90625" customWidth="1"/>
+    <col min="3" max="3" width="6.08984375" customWidth="1"/>
+    <col min="4" max="4" width="9.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" customWidth="1"/>
+    <col min="8" max="8" width="16.7265625" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="24" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="32" customWidth="1"/>
@@ -502,19 +618,19 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="B2">
         <v>1000</v>
       </c>
       <c r="C2">
-        <v>700</v>
+        <v>7000</v>
       </c>
       <c r="D2">
         <v>0.99540541735152699</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <v>1000</v>
@@ -523,42 +639,42 @@
         <v>10.000000000000259</v>
       </c>
       <c r="H2">
-        <v>692.09523809523853</v>
+        <v>378.79365079365118</v>
       </c>
       <c r="I2">
-        <v>692.09523809523853</v>
+        <v>378.79365079365118</v>
       </c>
       <c r="J2">
-        <v>84.015873015873069</v>
+        <v>49.333333333333371</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>73.818372999987332</v>
+        <v>982.53353290000814</v>
       </c>
       <c r="M2">
-        <v>0.10210619999270421</v>
+        <v>0.1346932000014931</v>
       </c>
       <c r="N2">
-        <v>73.920479199980036</v>
+        <v>982.66822610000963</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="B3">
         <v>1000</v>
       </c>
       <c r="C3">
-        <v>700</v>
+        <v>7000</v>
       </c>
       <c r="D3">
         <v>0.99540541735152699</v>
       </c>
       <c r="E3">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1000</v>
@@ -567,25 +683,25 @@
         <v>10.000000000000259</v>
       </c>
       <c r="H3">
-        <v>461.47619047619031</v>
+        <v>456.07936507936489</v>
       </c>
       <c r="I3">
-        <v>461.47619047619003</v>
+        <v>456.07936507936489</v>
       </c>
       <c r="J3">
-        <v>54.380952380952323</v>
+        <v>66.666666666666643</v>
       </c>
       <c r="K3">
-        <v>3.4106051316484809E-13</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>74.454383999996935</v>
+        <v>971.77427520000492</v>
       </c>
       <c r="M3">
-        <v>0.19750410001142879</v>
+        <v>0.13248980000207669</v>
       </c>
       <c r="N3">
-        <v>74.651888100008364</v>
+        <v>971.906765000007</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -596,45 +712,45 @@
         <v>1000</v>
       </c>
       <c r="C4">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="D4">
-        <v>0.9908319448927676</v>
+        <v>0.99540541735152699</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G4">
-        <v>10.00000000000014</v>
+        <v>10.000000000000259</v>
       </c>
       <c r="H4">
-        <v>1443.4920634920641</v>
+        <v>461.47619047619031</v>
       </c>
       <c r="I4">
-        <v>1443.4920634920641</v>
+        <v>461.47619047619003</v>
       </c>
       <c r="J4">
-        <v>191.50793650793651</v>
+        <v>54.380952380952323</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3.4106051316484809E-13</v>
       </c>
       <c r="L4">
-        <v>75.455485999991652</v>
+        <v>74.454383999996935</v>
       </c>
       <c r="M4">
-        <v>0.1236056999914581</v>
+        <v>0.19750410001142879</v>
       </c>
       <c r="N4">
-        <v>75.57909169998311</v>
+        <v>74.651888100008364</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="B5">
         <v>1000</v>
@@ -643,125 +759,125 @@
         <v>1400</v>
       </c>
       <c r="D5">
-        <v>0.9908319448927676</v>
+        <v>0.99907938998446177</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G5">
-        <v>10.00000000000014</v>
+        <v>10.000000000000281</v>
       </c>
       <c r="H5">
-        <v>877.65079365079396</v>
+        <v>477.74603174603169</v>
       </c>
       <c r="I5">
-        <v>877.65079365079396</v>
+        <v>477.74603174603169</v>
       </c>
       <c r="J5">
-        <v>107.06349206349211</v>
+        <v>60.095238095238088</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>75.459162200000719</v>
+        <v>753.20107039999857</v>
       </c>
       <c r="M5">
-        <v>9.8307799999020062E-2</v>
+        <v>0.1017596000019694</v>
       </c>
       <c r="N5">
-        <v>75.557469999999739</v>
+        <v>753.30283000000054</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="B6">
         <v>1000</v>
       </c>
       <c r="C6">
-        <v>7000</v>
+        <v>700</v>
       </c>
       <c r="D6">
-        <v>0.954992586021436</v>
+        <v>0.99953958900308781</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="G6">
-        <v>10.00000000000005</v>
+        <v>9.9999999999968345</v>
       </c>
       <c r="H6">
-        <v>856.49206349206236</v>
+        <v>590.28571428571365</v>
       </c>
       <c r="I6">
-        <v>856.49206349206213</v>
+        <v>590.28571428571365</v>
       </c>
       <c r="J6">
-        <v>97.539682539682389</v>
+        <v>71.587301587301525</v>
       </c>
       <c r="K6">
-        <v>2.2737367544323211E-13</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>72.138476599997375</v>
+        <v>744.27914169999713</v>
       </c>
       <c r="M6">
-        <v>0.19253570000000761</v>
+        <v>9.3901899992488325E-2</v>
       </c>
       <c r="N6">
-        <v>72.331012299997383</v>
+        <v>744.37304359998961</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>700000</v>
+        <v>7000000</v>
       </c>
       <c r="B7">
         <v>1000</v>
       </c>
       <c r="C7">
-        <v>7000</v>
+        <v>700</v>
       </c>
       <c r="D7">
-        <v>0.954992586021436</v>
+        <v>0.99953958900308781</v>
       </c>
       <c r="E7">
         <v>88</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="G7">
-        <v>10.00000000000005</v>
+        <v>9.9999999999968345</v>
       </c>
       <c r="H7">
-        <v>760.44444444444366</v>
+        <v>602.50793650793673</v>
       </c>
       <c r="I7">
-        <v>760.44444444444366</v>
+        <v>602.50793650793673</v>
       </c>
       <c r="J7">
-        <v>92.142857142857068</v>
+        <v>75.587301587301582</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>72.686234699998749</v>
+        <v>759.55909609999799</v>
       </c>
       <c r="M7">
-        <v>0.1007298000040464</v>
+        <v>0.1006599000102142</v>
       </c>
       <c r="N7">
-        <v>72.786964500002796</v>
+        <v>759.6597560000082</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -772,45 +888,45 @@
         <v>1000</v>
       </c>
       <c r="C8">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="D8">
-        <v>0.99953958900308781</v>
+        <v>0.99907938998446177</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G8">
-        <v>9.9999999999968345</v>
+        <v>10.000000000000281</v>
       </c>
       <c r="H8">
-        <v>590.28571428571365</v>
+        <v>681.85714285714232</v>
       </c>
       <c r="I8">
-        <v>590.28571428571365</v>
+        <v>681.85714285714232</v>
       </c>
       <c r="J8">
-        <v>71.587301587301525</v>
+        <v>81.158730158730094</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>744.27914169999713</v>
+        <v>864.83005029999185</v>
       </c>
       <c r="M8">
-        <v>9.3901899992488325E-2</v>
+        <v>0.12765330000547689</v>
       </c>
       <c r="N8">
-        <v>744.37304359998961</v>
+        <v>864.95770359999733</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>7000000</v>
+        <v>700000</v>
       </c>
       <c r="B9">
         <v>1000</v>
@@ -819,218 +935,524 @@
         <v>700</v>
       </c>
       <c r="D9">
-        <v>0.99953958900308781</v>
+        <v>0.99540541735152699</v>
       </c>
       <c r="E9">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G9">
-        <v>9.9999999999968345</v>
+        <v>10.000000000000259</v>
       </c>
       <c r="H9">
-        <v>602.50793650793673</v>
+        <v>692.09523809523853</v>
       </c>
       <c r="I9">
-        <v>602.50793650793673</v>
+        <v>692.09523809523853</v>
       </c>
       <c r="J9">
-        <v>75.587301587301582</v>
+        <v>84.015873015873069</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>759.55909609999799</v>
+        <v>73.818372999987332</v>
       </c>
       <c r="M9">
-        <v>0.1006599000102142</v>
+        <v>0.10210619999270421</v>
       </c>
       <c r="N9">
-        <v>759.6597560000082</v>
+        <v>73.920479199980036</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>7000000</v>
+        <v>700000</v>
       </c>
       <c r="B10">
         <v>1000</v>
       </c>
       <c r="C10">
-        <v>1400</v>
+        <v>7000</v>
       </c>
       <c r="D10">
-        <v>0.99907938998446177</v>
+        <v>0.954992586021436</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F10">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>10.000000000000281</v>
+        <v>10.00000000000005</v>
       </c>
       <c r="H10">
-        <v>477.74603174603169</v>
+        <v>760.44444444444366</v>
       </c>
       <c r="I10">
-        <v>477.74603174603169</v>
+        <v>760.44444444444366</v>
       </c>
       <c r="J10">
-        <v>60.095238095238088</v>
+        <v>92.142857142857068</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>753.20107039999857</v>
+        <v>72.686234699998749</v>
       </c>
       <c r="M10">
-        <v>0.1017596000019694</v>
+        <v>0.1007298000040464</v>
       </c>
       <c r="N10">
-        <v>753.30283000000054</v>
+        <v>72.786964500002796</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>7000000</v>
+        <v>700000</v>
       </c>
       <c r="B11">
         <v>1000</v>
       </c>
       <c r="C11">
-        <v>1400</v>
+        <v>7000</v>
       </c>
       <c r="D11">
-        <v>0.99907938998446177</v>
+        <v>0.954992586021436</v>
       </c>
       <c r="E11">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>10.000000000000281</v>
+        <v>10.00000000000005</v>
       </c>
       <c r="H11">
-        <v>681.85714285714232</v>
+        <v>856.49206349206236</v>
       </c>
       <c r="I11">
-        <v>681.85714285714232</v>
+        <v>856.49206349206213</v>
       </c>
       <c r="J11">
-        <v>81.158730158730094</v>
+        <v>97.539682539682389</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2.2737367544323211E-13</v>
       </c>
       <c r="L11">
-        <v>864.83005029999185</v>
+        <v>72.138476599997375</v>
       </c>
       <c r="M11">
-        <v>0.12765330000547689</v>
+        <v>0.19253570000000761</v>
       </c>
       <c r="N11">
-        <v>864.95770359999733</v>
+        <v>72.331012299997383</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>7000000</v>
+        <v>700000</v>
       </c>
       <c r="B12">
         <v>1000</v>
       </c>
       <c r="C12">
-        <v>7000</v>
+        <v>1400</v>
       </c>
       <c r="D12">
-        <v>0.99540541735152699</v>
+        <v>0.9908319448927676</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F12">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G12">
-        <v>10.000000000000259</v>
+        <v>10.00000000000014</v>
       </c>
       <c r="H12">
-        <v>456.07936507936489</v>
+        <v>877.65079365079396</v>
       </c>
       <c r="I12">
-        <v>456.07936507936489</v>
+        <v>877.65079365079396</v>
       </c>
       <c r="J12">
-        <v>66.666666666666643</v>
+        <v>107.06349206349211</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>971.77427520000492</v>
+        <v>75.459162200000719</v>
       </c>
       <c r="M12">
-        <v>0.13248980000207669</v>
+        <v>9.8307799999020062E-2</v>
       </c>
       <c r="N12">
-        <v>971.906765000007</v>
+        <v>75.557469999999739</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13">
+        <v>700000</v>
+      </c>
+      <c r="B13">
+        <v>1000</v>
+      </c>
+      <c r="C13">
+        <v>1400</v>
+      </c>
+      <c r="D13">
+        <v>0.9908319448927676</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>500</v>
+      </c>
+      <c r="G13">
+        <v>10.00000000000014</v>
+      </c>
+      <c r="H13">
+        <v>1443.4920634920641</v>
+      </c>
+      <c r="I13">
+        <v>1443.4920634920641</v>
+      </c>
+      <c r="J13">
+        <v>191.50793650793651</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>75.455485999991652</v>
+      </c>
+      <c r="M13">
+        <v>0.1236056999914581</v>
+      </c>
+      <c r="N13">
+        <v>75.57909169998311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B16" s="1">
         <v>7000000</v>
       </c>
-      <c r="B13">
-        <v>1000</v>
-      </c>
-      <c r="C13">
+      <c r="C16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="1">
         <v>7000</v>
       </c>
-      <c r="D13">
+      <c r="E16" s="3">
         <v>0.99540541735152699</v>
       </c>
-      <c r="E13">
+      <c r="F16" s="1">
         <v>88</v>
       </c>
-      <c r="F13">
-        <v>1000</v>
-      </c>
-      <c r="G13">
-        <v>10.000000000000259</v>
-      </c>
-      <c r="H13">
+      <c r="G16" s="2">
         <v>378.79365079365118</v>
       </c>
-      <c r="I13">
-        <v>378.79365079365118</v>
-      </c>
-      <c r="J13">
-        <v>49.333333333333371</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>982.53353290000814</v>
-      </c>
-      <c r="M13">
-        <v>0.1346932000014931</v>
-      </c>
-      <c r="N13">
+      <c r="H16" s="2">
         <v>982.66822610000963</v>
       </c>
     </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B17" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="1">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.99540541735152699</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>456.07936507936489</v>
+      </c>
+      <c r="H17" s="2">
+        <v>971.906765000007</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="1">
+        <v>700000</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D18" s="1">
+        <v>700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.99540541735152699</v>
+      </c>
+      <c r="F18" s="1">
+        <v>88</v>
+      </c>
+      <c r="G18" s="2">
+        <v>461.47619047619003</v>
+      </c>
+      <c r="H18" s="2">
+        <v>74.651888100008364</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1400</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.99907938998446177</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>477.74603174603169</v>
+      </c>
+      <c r="H19" s="2">
+        <v>753.30283000000054</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="1">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.99953958900308781</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>590.28571428571365</v>
+      </c>
+      <c r="H20" s="2">
+        <v>744.37304359998961</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="1">
+        <v>700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.99953958900308781</v>
+      </c>
+      <c r="F21" s="1">
+        <v>88</v>
+      </c>
+      <c r="G21" s="2">
+        <v>602.50793650793673</v>
+      </c>
+      <c r="H21" s="2">
+        <v>759.6597560000082</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.99907938998446177</v>
+      </c>
+      <c r="F22" s="1">
+        <v>88</v>
+      </c>
+      <c r="G22" s="2">
+        <v>681.85714285714232</v>
+      </c>
+      <c r="H22" s="2">
+        <v>864.95770359999733</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="1">
+        <v>700000</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D23" s="1">
+        <v>700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.99540541735152699</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>692.09523809523853</v>
+      </c>
+      <c r="H23" s="2">
+        <v>73.920479199980036</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="1">
+        <v>700000</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D24" s="1">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.954992586021436</v>
+      </c>
+      <c r="F24" s="1">
+        <v>88</v>
+      </c>
+      <c r="G24" s="2">
+        <v>760.44444444444366</v>
+      </c>
+      <c r="H24" s="2">
+        <v>72.786964500002796</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="1">
+        <v>700000</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="1">
+        <v>7000</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.954992586021436</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>856.49206349206213</v>
+      </c>
+      <c r="H25" s="2">
+        <v>72.331012299997383</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1">
+        <v>700000</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.9908319448927676</v>
+      </c>
+      <c r="F26" s="1">
+        <v>88</v>
+      </c>
+      <c r="G26" s="2">
+        <v>877.65079365079396</v>
+      </c>
+      <c r="H26" s="2">
+        <v>75.557469999999739</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="1">
+        <v>700000</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.9908319448927676</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1443.4920634920641</v>
+      </c>
+      <c r="H27" s="2">
+        <v>75.57909169998311</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:N13" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N13">
+      <sortCondition ref="H1:H13"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1414,7 +1836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1422,10 +1844,13 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" customWidth="1"/>
+    <col min="7" max="7" width="27.54296875" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" customWidth="1"/>
+    <col min="10" max="10" width="12.26953125" customWidth="1"/>
+    <col min="11" max="11" width="12.7265625" customWidth="1"/>
+    <col min="12" max="12" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="32" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
   </cols>
@@ -2002,8 +2427,149 @@
         <v>75.57909169998311</v>
       </c>
     </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="F16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F17" s="1">
+        <v>88</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H17" s="1">
+        <v>10.000000000000259</v>
+      </c>
+      <c r="I17" s="2">
+        <v>378.79365079365118</v>
+      </c>
+      <c r="J17" s="2">
+        <v>378.79365079365118</v>
+      </c>
+      <c r="K17" s="2">
+        <v>982.53353290000814</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.1346932000014931</v>
+      </c>
+    </row>
+    <row r="18" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10.000000000000259</v>
+      </c>
+      <c r="I18" s="2">
+        <v>456.07936507936489</v>
+      </c>
+      <c r="J18" s="2">
+        <v>456.07936507936489</v>
+      </c>
+      <c r="K18" s="2">
+        <v>971.77427520000492</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0.13248980000207669</v>
+      </c>
+    </row>
+    <row r="19" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F19" s="1">
+        <v>88</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="1">
+        <v>10.000000000000259</v>
+      </c>
+      <c r="I19" s="2">
+        <v>461.47619047619031</v>
+      </c>
+      <c r="J19" s="2">
+        <v>461.47619047619003</v>
+      </c>
+      <c r="K19" s="2">
+        <v>74.454383999996935</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.19750410001142879</v>
+      </c>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H20" s="1">
+        <v>10.000000000000281</v>
+      </c>
+      <c r="I20" s="2">
+        <v>477.74603174603169</v>
+      </c>
+      <c r="J20" s="2">
+        <v>477.74603174603169</v>
+      </c>
+      <c r="K20" s="2">
+        <v>753.20107039999857</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.1017596000019694</v>
+      </c>
+    </row>
+    <row r="21" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="1">
+        <v>9.9999999999968345</v>
+      </c>
+      <c r="I21" s="2">
+        <v>590.28571428571365</v>
+      </c>
+      <c r="J21" s="2">
+        <v>590.28571428571365</v>
+      </c>
+      <c r="K21" s="2">
+        <v>744.27914169999713</v>
+      </c>
+      <c r="L21" s="2">
+        <v>9.3901899992488325E-2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N13" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>